--- a/apps/server-web/public/student-batch-template.xlsx
+++ b/apps/server-web/public/student-batch-template.xlsx
@@ -334,7 +334,7 @@
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
